--- a/06_支撑材料/result1.xlsx
+++ b/06_支撑材料/result1.xlsx
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>902.691967</v>
+        <v>569.3586330000001</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>571.615383</v>
+        <v>904.948717</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
